--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117857037</v>
+        <v>118087774</v>
       </c>
       <c r="B2" t="n">
-        <v>100097</v>
+        <v>57990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500029</v>
+        <v>499927</v>
       </c>
       <c r="R2" t="n">
-        <v>6545537</v>
+        <v>6545569</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>enstaka</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117857023</v>
+        <v>117857036</v>
       </c>
       <c r="B3" t="n">
-        <v>57303</v>
+        <v>103338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500319</v>
+        <v>500122</v>
       </c>
       <c r="R3" t="n">
-        <v>6545484</v>
+        <v>6545543</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117857036</v>
+        <v>117857023</v>
       </c>
       <c r="B4" t="n">
-        <v>103338</v>
+        <v>57303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500122</v>
+        <v>500319</v>
       </c>
       <c r="R4" t="n">
-        <v>6545543</v>
+        <v>6545484</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +968,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +992,431 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117857037</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100097</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6545537</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118087758</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57438</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500256</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6545531</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118087776</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57438</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500250</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6545592</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118087775</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57438</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499945</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6545549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118087774</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117857036</v>
+        <v>117857037</v>
       </c>
       <c r="B3" t="n">
-        <v>103338</v>
+        <v>100099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500122</v>
+        <v>500029</v>
       </c>
       <c r="R3" t="n">
-        <v>6545543</v>
+        <v>6545537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +891,7 @@
         <v>117857023</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117857037</v>
+        <v>117857036</v>
       </c>
       <c r="B5" t="n">
-        <v>100097</v>
+        <v>103340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500029</v>
+        <v>500122</v>
       </c>
       <c r="R5" t="n">
-        <v>6545537</v>
+        <v>6545543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118087758</v>
+        <v>118087775</v>
       </c>
       <c r="B6" t="n">
-        <v>57438</v>
+        <v>57439</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500256</v>
+        <v>499945</v>
       </c>
       <c r="R6" t="n">
-        <v>6545531</v>
+        <v>6545549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118087776</v>
+        <v>118087758</v>
       </c>
       <c r="B7" t="n">
-        <v>57438</v>
+        <v>57439</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500250</v>
+        <v>500256</v>
       </c>
       <c r="R7" t="n">
-        <v>6545592</v>
+        <v>6545531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118087775</v>
+        <v>118087776</v>
       </c>
       <c r="B8" t="n">
-        <v>57438</v>
+        <v>57439</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499945</v>
+        <v>500250</v>
       </c>
       <c r="R8" t="n">
-        <v>6545549</v>
+        <v>6545592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129530892</v>
       </c>
       <c r="B3" t="n">
-        <v>56603</v>
+        <v>56608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129530894</v>
       </c>
       <c r="B4" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129531071</v>
+        <v>129530890</v>
       </c>
       <c r="B5" t="n">
-        <v>56610</v>
+        <v>56620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,26 +1044,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499907</v>
+        <v>499909</v>
       </c>
       <c r="R5" t="n">
-        <v>6545648</v>
+        <v>6545644</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129530890</v>
+        <v>129531071</v>
       </c>
       <c r="B6" t="n">
         <v>56615</v>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499909</v>
+        <v>499907</v>
       </c>
       <c r="R6" t="n">
-        <v>6545644</v>
+        <v>6545648</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1288,7 @@
         <v>129530891</v>
       </c>
       <c r="B7" t="n">
-        <v>56610</v>
+        <v>56615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>129525978</v>
       </c>
       <c r="B15" t="n">
-        <v>56603</v>
+        <v>56608</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>129530974</v>
       </c>
       <c r="B16" t="n">
-        <v>56610</v>
+        <v>56615</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>129531085</v>
       </c>
       <c r="B17" t="n">
-        <v>56615</v>
+        <v>56620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129525977</v>
       </c>
       <c r="B18" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129525976</v>
       </c>
       <c r="B19" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129530892</v>
       </c>
       <c r="B3" t="n">
-        <v>56608</v>
+        <v>56609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129530894</v>
       </c>
       <c r="B4" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129530890</v>
+        <v>129531071</v>
       </c>
       <c r="B5" t="n">
-        <v>56620</v>
+        <v>56616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,26 +1044,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499909</v>
+        <v>499907</v>
       </c>
       <c r="R5" t="n">
-        <v>6545644</v>
+        <v>6545648</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129531071</v>
+        <v>129530890</v>
       </c>
       <c r="B6" t="n">
-        <v>56615</v>
+        <v>56621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499907</v>
+        <v>499909</v>
       </c>
       <c r="R6" t="n">
-        <v>6545648</v>
+        <v>6545644</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1288,7 @@
         <v>129530891</v>
       </c>
       <c r="B7" t="n">
-        <v>56615</v>
+        <v>56616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>129525978</v>
       </c>
       <c r="B15" t="n">
-        <v>56608</v>
+        <v>56609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>129530974</v>
       </c>
       <c r="B16" t="n">
-        <v>56615</v>
+        <v>56616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>129531085</v>
       </c>
       <c r="B17" t="n">
-        <v>56620</v>
+        <v>56621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129525977</v>
       </c>
       <c r="B18" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129525976</v>
       </c>
       <c r="B19" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129531071</v>
+        <v>129530890</v>
       </c>
       <c r="B5" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,26 +1044,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499907</v>
+        <v>499909</v>
       </c>
       <c r="R5" t="n">
-        <v>6545648</v>
+        <v>6545644</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129530890</v>
+        <v>129531071</v>
       </c>
       <c r="B6" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499909</v>
+        <v>499907</v>
       </c>
       <c r="R6" t="n">
-        <v>6545644</v>
+        <v>6545648</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129530890</v>
+        <v>129531071</v>
       </c>
       <c r="B5" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,26 +1044,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499909</v>
+        <v>499907</v>
       </c>
       <c r="R5" t="n">
-        <v>6545644</v>
+        <v>6545648</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129531071</v>
+        <v>129530890</v>
       </c>
       <c r="B6" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499907</v>
+        <v>499909</v>
       </c>
       <c r="R6" t="n">
-        <v>6545648</v>
+        <v>6545644</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118087774</v>
+        <v>117857023</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499927</v>
+        <v>500319</v>
       </c>
       <c r="R2" t="n">
-        <v>6545569</v>
+        <v>6545484</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129530892</v>
+        <v>129530891</v>
       </c>
       <c r="B3" t="n">
-        <v>56609</v>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,26 +788,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -907,37 +903,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129530894</v>
+        <v>129530974</v>
       </c>
       <c r="B4" t="n">
-        <v>56602</v>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -961,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499909</v>
+        <v>500144</v>
       </c>
       <c r="R4" t="n">
-        <v>6545644</v>
+        <v>6545544</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,7 +1032,7 @@
         <v>129531071</v>
       </c>
       <c r="B5" t="n">
-        <v>56616</v>
+        <v>56830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,52 +1155,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129530890</v>
+        <v>118087758</v>
       </c>
       <c r="B6" t="n">
-        <v>56621</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1213,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499909</v>
+        <v>500256</v>
       </c>
       <c r="R6" t="n">
-        <v>6545644</v>
+        <v>6545531</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,22 +1224,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,64 +1244,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129530891</v>
+        <v>118087775</v>
       </c>
       <c r="B7" t="n">
-        <v>56616</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1339,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499909</v>
+        <v>499945</v>
       </c>
       <c r="R7" t="n">
-        <v>6545644</v>
+        <v>6545549</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1325,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,27 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117857023</v>
+        <v>118087776</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,16 +1368,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1444,20 +1385,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500319</v>
+        <v>500250</v>
       </c>
       <c r="R8" t="n">
-        <v>6545484</v>
+        <v>6545592</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,17 +1426,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,62 +1446,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117857037</v>
+        <v>118087774</v>
       </c>
       <c r="B9" t="n">
-        <v>100101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500029</v>
+        <v>499927</v>
       </c>
       <c r="R9" t="n">
-        <v>6545537</v>
+        <v>6545569</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,17 +1527,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>enstaka</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,27 +1547,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117857036</v>
+        <v>118087757</v>
       </c>
       <c r="B10" t="n">
-        <v>103343</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,34 +1570,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500122</v>
+        <v>500488</v>
       </c>
       <c r="R10" t="n">
-        <v>6545543</v>
+        <v>6545554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,17 +1628,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,49 +1648,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118087776</v>
+        <v>129525978</v>
       </c>
       <c r="B11" t="n">
-        <v>57441</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1770,19 +1693,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500250</v>
+        <v>500160</v>
       </c>
       <c r="R11" t="n">
-        <v>6545592</v>
+        <v>6545472</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,12 +1744,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,54 +1774,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118087775</v>
+        <v>129530892</v>
       </c>
       <c r="B12" t="n">
-        <v>57441</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103020</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499945</v>
+        <v>499909</v>
       </c>
       <c r="R12" t="n">
-        <v>6545549</v>
+        <v>6545644</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,12 +1870,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,54 +1900,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118087758</v>
+        <v>129530890</v>
       </c>
       <c r="B13" t="n">
-        <v>57441</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1988,13 +1966,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500256</v>
+        <v>499909</v>
       </c>
       <c r="R13" t="n">
-        <v>6545531</v>
+        <v>6545644</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,12 +1996,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,27 +2026,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124576144</v>
+        <v>129531085</v>
       </c>
       <c r="B14" t="n">
-        <v>58373</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,46 +2049,56 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Handberga, Nrk</t>
+          <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500342</v>
+        <v>500152</v>
       </c>
       <c r="R14" t="n">
-        <v>6545720</v>
+        <v>6545553</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2129,22 +2122,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,44 +2152,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129525978</v>
+        <v>129525976</v>
       </c>
       <c r="B15" t="n">
-        <v>56609</v>
+        <v>56816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2225,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500160</v>
+        <v>500058</v>
       </c>
       <c r="R15" t="n">
-        <v>6545472</v>
+        <v>6545549</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2297,37 +2290,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129530974</v>
+        <v>129525977</v>
       </c>
       <c r="B16" t="n">
-        <v>56616</v>
+        <v>56816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2342,7 +2335,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>detektor med heterodyn och tidsexpansion</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2351,10 +2344,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500144</v>
+        <v>500042</v>
       </c>
       <c r="R16" t="n">
-        <v>6545544</v>
+        <v>6545456</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2381,22 +2374,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,37 +2416,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129531085</v>
+        <v>129525982</v>
       </c>
       <c r="B17" t="n">
-        <v>56621</v>
+        <v>56816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2468,7 +2461,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>detektor med heterodyn och tidsexpansion</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2477,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500152</v>
+        <v>499903</v>
       </c>
       <c r="R17" t="n">
-        <v>6545553</v>
+        <v>6545607</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2507,22 +2500,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2549,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129525977</v>
+        <v>129530894</v>
       </c>
       <c r="B18" t="n">
-        <v>56602</v>
+        <v>56816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2572,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2594,7 +2587,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>detektor med heterodyn och tidsexpansion</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2603,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500042</v>
+        <v>499909</v>
       </c>
       <c r="R18" t="n">
-        <v>6545456</v>
+        <v>6545644</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2633,22 +2626,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2675,32 +2668,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129525976</v>
+        <v>124576144</v>
       </c>
       <c r="B19" t="n">
-        <v>56602</v>
+        <v>58817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2708,34 +2701,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>detektor med heterodyn och tidsexpansion</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sållaretorp, Nrk</t>
+          <t>Handberga, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500058</v>
+        <v>500342</v>
       </c>
       <c r="R19" t="n">
-        <v>6545549</v>
+        <v>6545720</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2759,22 +2742,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2789,15 +2772,321 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117857035</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500403</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6545581</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117857036</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>500122</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6545543</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>117857037</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6545537</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46392-2023 artfynd.xlsx
+++ b/artfynd/A 46392-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530891</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530974</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087775</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087774</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1504,6 +1539,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530892</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530890</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1756,6 +1801,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531085</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1882,6 +1932,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525976</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2008,6 +2063,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525977</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2134,6 +2194,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525982</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2260,6 +2325,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530894</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2362,6 +2432,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117857036</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2464,6 +2539,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117857037</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2566,6 +2646,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117857023</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2667,6 +2752,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087758</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2768,6 +2858,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087776</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2869,6 +2964,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087757</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2985,6 +3085,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124576144</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3087,8 +3192,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117857035</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>